--- a/output/pdf_financials_xlsx/MTTA.xlsx
+++ b/output/pdf_financials_xlsx/MTTA.xlsx
@@ -2205,16 +2205,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.7302</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.397704</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.2151</v>
       </c>
     </row>
     <row r="93">
@@ -2690,7 +2690,7 @@
         <v>-0.0128</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>-0.154922</v>
+        <v>-0.329118</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>-0.410563</v>
@@ -3630,7 +3630,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4038,7 +4042,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -4436,7 +4444,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>0.7302</v>
       </c>
@@ -6120,7 +6132,11 @@
           <t>Exploration and evaluation expenses</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MTTA.xlsx
+++ b/output/pdf_financials_xlsx/MTTA.xlsx
@@ -604,13 +604,13 @@
         <v>0.117887</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.121523</v>
+        <v>0.306562</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.480996</v>
+        <v>2.328851</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.215804</v>
+        <v>2.052581</v>
       </c>
     </row>
     <row r="11">
@@ -626,10 +626,10 @@
         <v>-0.306562</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.480996</v>
+        <v>-2.328851</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.215804</v>
+        <v>-2.052581</v>
       </c>
     </row>
     <row r="12">
@@ -642,13 +642,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002039</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.058937</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.039515</v>
       </c>
     </row>
     <row r="13">
@@ -945,13 +945,13 @@
         <v>-0.124073</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.304678</v>
+        <v>-0.306717</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.660959</v>
+        <v>-2.719896</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.656096</v>
+        <v>-1.695611</v>
       </c>
     </row>
     <row r="28">
@@ -983,13 +983,13 @@
         <v>-0.124073</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.304678</v>
+        <v>-0.306717</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.660959</v>
+        <v>-2.719896</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.656096</v>
+        <v>-1.695611</v>
       </c>
     </row>
     <row r="30">
@@ -1079,16 +1079,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.612492</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.045424</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.358392</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.427777</v>
       </c>
     </row>
     <row r="35">
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.612492</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.045424</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.358392</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.427777</v>
       </c>
     </row>
     <row r="37">
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.612492</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.057718</v>
+        <v>0.012294</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.511415</v>
+        <v>0.153023</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.76425</v>
+        <v>0.336473</v>
       </c>
     </row>
     <row r="49">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
@@ -5206,7 +5206,11 @@
           <t>Refund of reclamation deposit</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -7388,7 +7392,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7397,13 +7401,13 @@
         </is>
       </c>
       <c r="F121" s="5" t="n">
-        <v>-0.306562</v>
+        <v>0.306562</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>-2.328851</v>
+        <v>2.328851</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>-2.052581</v>
+        <v>2.052581</v>
       </c>
     </row>
     <row r="122">
@@ -7424,7 +7428,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8584,7 +8588,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">

--- a/output/pdf_financials_xlsx/MTTA.xlsx
+++ b/output/pdf_financials_xlsx/MTTA.xlsx
@@ -1714,16 +1714,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.014583</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.075533</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.069435</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.144836</v>
       </c>
     </row>
     <row r="68">
@@ -5748,7 +5748,11 @@
           <t>Finder’s warrants issued in connection with private placement</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -5782,7 +5786,11 @@
           <t>Finders’ shares issued in connection with private placement</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -6430,7 +6438,11 @@
           <t>Finder’s warrants issued in connection with private placement</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
